--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -13,16 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_efficient_natural_gas_residential" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_baseline_natural_gas_residential" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_existing_natural_gas_residential" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="central_ac_efficient_electric_residential" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="central_ac_baseline_electric_residential" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="central_ac_existing_electric_residential" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="room_ac_efficient_electric_residential" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="room_ac_baseline_electric_residential" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="room_ac_existing_electric_residential" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_efficient_electric_residential" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_baseline_electric_residential" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_top10_electric_residential" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_existing_electric_residential" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_efficient_electric_residential" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_baseline_electric_residential" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_top10_electric_residential" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_existing_electric_residential" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1850,4290 +1844,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>parent_condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>efficiency_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>efficiency_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>year_start_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>year_end_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>unit_of_characterization</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>competition_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_or_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>base_building_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>interaction_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>equipment_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>equipment_cost_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>labor_cost_installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>effective_useful_life_yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>water_usage_gal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o_and_m_costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>secondary_hvac_heating_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>secondary_hvac_cooling_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>climate_zone_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RET_retirement_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RET_add_on_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RET_ER_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NC_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ROB_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RENO_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>equipment_savings_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fuel-end_use_combinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fuel_01_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fuel_01_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fuel_01_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fuel_01_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fuel_02_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fuel_02_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fuel_02_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fuel_02_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fuel_03_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fuel_03_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuel_03_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fuel_03_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fuel_04_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fuel_04_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fuel_04_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fuel_04_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_05_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_05_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fuel_05_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fuel_05_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fuel_06_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fuel_06_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fuel_06_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fuel_06_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fuel_07_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fuel_07_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fuel_07_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fuel_07_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fuel_08_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fuel_08_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fuel_08_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fuel_08_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fuel_09_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fuel_09_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fuel_09_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fuel_09_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>fuel_10_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fuel_10_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fuel_10_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fuel_10_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fuel_11_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_11_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fuel_11_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fuel_11_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fuel_12_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fuel_12_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fuel_12_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>fuel_12_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>fuel_13_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fuel_13_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fuel_13_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fuel_13_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fuel_14_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>fuel_14_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>fuel_14_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>fuel_14_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>fuel_15_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>fuel_15_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>fuel_15_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fuel_15_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>fuel_16_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>fuel_16_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>fuel_16_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fuel_16_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fuel_17_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fuel_17_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fuel_17_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>fuel_17_end_use</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>parent_condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>efficiency_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>efficiency_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>year_start_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>year_end_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>unit_of_characterization</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>competition_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_or_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>base_building_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>interaction_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>equipment_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>equipment_cost_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>labor_cost_installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>effective_useful_life_yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>water_usage_gal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o_and_m_costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>secondary_hvac_heating_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>secondary_hvac_cooling_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>climate_zone_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RET_retirement_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RET_add_on_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RET_ER_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NC_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ROB_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RENO_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>equipment_savings_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fuel-end_use_combinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fuel_01_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fuel_01_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fuel_01_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fuel_01_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fuel_02_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fuel_02_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fuel_02_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fuel_02_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fuel_03_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fuel_03_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuel_03_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fuel_03_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fuel_04_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fuel_04_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fuel_04_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fuel_04_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_05_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_05_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fuel_05_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fuel_05_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fuel_06_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fuel_06_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fuel_06_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fuel_06_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fuel_07_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fuel_07_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fuel_07_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fuel_07_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fuel_08_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fuel_08_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fuel_08_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fuel_08_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fuel_09_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fuel_09_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fuel_09_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fuel_09_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>fuel_10_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fuel_10_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fuel_10_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fuel_10_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fuel_11_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_11_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fuel_11_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fuel_11_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fuel_12_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fuel_12_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fuel_12_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>fuel_12_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>fuel_13_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fuel_13_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fuel_13_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fuel_13_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fuel_14_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>fuel_14_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>fuel_14_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>fuel_14_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>fuel_15_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>fuel_15_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>fuel_15_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fuel_15_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>fuel_16_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>fuel_16_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>fuel_16_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fuel_16_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fuel_17_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fuel_17_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fuel_17_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>fuel_17_end_use</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>parent_condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>efficiency_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>efficiency_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>year_start_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>year_end_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>unit_of_characterization</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>competition_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_or_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>base_building_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>interaction_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>equipment_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>equipment_cost_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>labor_cost_installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>effective_useful_life_yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>water_usage_gal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o_and_m_costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>secondary_hvac_heating_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>secondary_hvac_cooling_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>climate_zone_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RET_retirement_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RET_add_on_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RET_ER_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NC_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ROB_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RENO_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>equipment_savings_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fuel-end_use_combinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fuel_01_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fuel_01_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fuel_01_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fuel_01_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fuel_02_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fuel_02_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fuel_02_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fuel_02_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fuel_03_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fuel_03_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuel_03_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fuel_03_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fuel_04_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fuel_04_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fuel_04_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fuel_04_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_05_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_05_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fuel_05_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fuel_05_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fuel_06_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fuel_06_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fuel_06_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fuel_06_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fuel_07_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fuel_07_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fuel_07_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fuel_07_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fuel_08_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fuel_08_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fuel_08_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fuel_08_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fuel_09_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fuel_09_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fuel_09_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fuel_09_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>fuel_10_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fuel_10_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fuel_10_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fuel_10_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fuel_11_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_11_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fuel_11_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fuel_11_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fuel_12_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fuel_12_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fuel_12_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>fuel_12_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>fuel_13_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fuel_13_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fuel_13_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fuel_13_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fuel_14_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>fuel_14_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>fuel_14_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>fuel_14_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>fuel_15_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>fuel_15_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>fuel_15_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fuel_15_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>fuel_16_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>fuel_16_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>fuel_16_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fuel_16_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fuel_17_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fuel_17_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fuel_17_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>fuel_17_end_use</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>parent_condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>efficiency_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>efficiency_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>year_start_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>year_end_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>unit_of_characterization</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>competition_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_or_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>base_building_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>interaction_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>equipment_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>equipment_cost_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>labor_cost_installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>effective_useful_life_yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>water_usage_gal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o_and_m_costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>secondary_hvac_heating_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>secondary_hvac_cooling_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>climate_zone_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RET_retirement_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RET_add_on_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RET_ER_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NC_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ROB_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RENO_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>equipment_savings_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fuel-end_use_combinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fuel_01_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fuel_01_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fuel_01_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fuel_01_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fuel_02_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fuel_02_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fuel_02_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fuel_02_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fuel_03_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fuel_03_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuel_03_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fuel_03_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fuel_04_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fuel_04_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fuel_04_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fuel_04_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_05_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_05_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fuel_05_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fuel_05_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fuel_06_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fuel_06_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fuel_06_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fuel_06_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fuel_07_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fuel_07_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fuel_07_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fuel_07_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fuel_08_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fuel_08_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fuel_08_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fuel_08_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fuel_09_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fuel_09_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fuel_09_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fuel_09_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>fuel_10_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fuel_10_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fuel_10_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fuel_10_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fuel_11_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_11_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fuel_11_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fuel_11_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fuel_12_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fuel_12_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fuel_12_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>fuel_12_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>fuel_13_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fuel_13_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fuel_13_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fuel_13_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fuel_14_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>fuel_14_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>fuel_14_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>fuel_14_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>fuel_15_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>fuel_15_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>fuel_15_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fuel_15_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>fuel_16_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>fuel_16_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>fuel_16_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fuel_16_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fuel_17_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fuel_17_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fuel_17_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>fuel_17_end_use</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>parent_condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>efficiency_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>efficiency_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>year_start_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>year_end_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>unit_of_characterization</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>competition_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_or_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>base_building_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>interaction_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>equipment_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>equipment_cost_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>labor_cost_installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>effective_useful_life_yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>water_usage_gal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o_and_m_costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>secondary_hvac_heating_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>secondary_hvac_cooling_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>climate_zone_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RET_retirement_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RET_add_on_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RET_ER_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NC_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ROB_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RENO_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>equipment_savings_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fuel-end_use_combinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fuel_01_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fuel_01_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fuel_01_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fuel_01_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fuel_02_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fuel_02_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fuel_02_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fuel_02_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fuel_03_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fuel_03_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuel_03_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fuel_03_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fuel_04_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fuel_04_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fuel_04_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fuel_04_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_05_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_05_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fuel_05_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fuel_05_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fuel_06_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fuel_06_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fuel_06_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fuel_06_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fuel_07_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fuel_07_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fuel_07_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fuel_07_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fuel_08_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fuel_08_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fuel_08_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fuel_08_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fuel_09_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fuel_09_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fuel_09_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fuel_09_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>fuel_10_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fuel_10_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fuel_10_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fuel_10_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fuel_11_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_11_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fuel_11_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fuel_11_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fuel_12_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fuel_12_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fuel_12_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>fuel_12_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>fuel_13_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fuel_13_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fuel_13_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fuel_13_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fuel_14_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>fuel_14_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>fuel_14_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>fuel_14_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>fuel_15_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>fuel_15_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>fuel_15_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fuel_15_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>fuel_16_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>fuel_16_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>fuel_16_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fuel_16_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fuel_17_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fuel_17_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fuel_17_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>fuel_17_end_use</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>parent_condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_fuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>efficiency_description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>efficiency_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>year_start_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>year_end_baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>unit_of_characterization</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>competition_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_or_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>base_building_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>interaction_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>equipment_cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>equipment_cost_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>labor_cost_installation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>effective_useful_life_yrs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>water_usage_gal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>o_and_m_costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>secondary_hvac_heating_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>secondary_hvac_cooling_effect_flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>climate_zone_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RET_retirement_rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RET_add_on_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RET_ER_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NC_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ROB_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RENO_applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>equipment_savings_scale_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fuel-end_use_combinations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fuel_01_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fuel_01_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fuel_01_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fuel_01_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fuel_02_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fuel_02_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fuel_02_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fuel_02_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fuel_03_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fuel_03_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuel_03_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fuel_03_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fuel_04_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fuel_04_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fuel_04_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fuel_04_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_05_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_05_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fuel_05_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fuel_05_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>fuel_06_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>fuel_06_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fuel_06_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>fuel_06_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>fuel_07_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>fuel_07_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>fuel_07_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>fuel_07_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>fuel_08_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>fuel_08_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>fuel_08_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>fuel_08_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>fuel_09_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>fuel_09_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>fuel_09_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>fuel_09_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>fuel_10_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fuel_10_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fuel_10_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fuel_10_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fuel_11_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>fuel_11_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fuel_11_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fuel_11_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fuel_12_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>fuel_12_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fuel_12_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>fuel_12_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>fuel_13_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fuel_13_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fuel_13_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fuel_13_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>fuel_14_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>fuel_14_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>fuel_14_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>fuel_14_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>fuel_15_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>fuel_15_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>fuel_15_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>fuel_15_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>fuel_16_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>fuel_16_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>fuel_16_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fuel_16_end_use</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fuel_17_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fuel_17_consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fuel_17_units</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>fuel_17_end_use</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_efficient_oil_residential" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_baseline_oil_residential" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_existing_oil_residential" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_efficient_natural_gas_residential" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_baseline_natural_gas_residential" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_existing_natural_gas_residential" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_efficient_electric_residential" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_baseline_electric_residential" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_top10_electric_residential" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_existing_electric_residential" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_efficient_residential" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_baseline_residential" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_existing_residential" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_efficient_residential" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_baseline_residential" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_existing_residential" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_efficient_residential" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_baseline_residential" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_top10_residential" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_existing_residential" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_efficient_residential" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_baseline_residential" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_existing_residential" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_efficient_residential" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_baseline_residential" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_top10_residential" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fridge_electric_existing_residential" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_efficient_residential" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_baseline_residential" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_top10_residential" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_existing_residential" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,6 +431,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -438,6 +443,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -445,6 +451,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -452,6 +463,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -459,6 +475,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -466,6 +483,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -473,6 +495,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -480,6 +503,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,6 +511,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -494,6 +523,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -501,6 +535,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -508,6 +547,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -515,6 +555,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -522,6 +567,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -529,6 +575,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -536,6 +583,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -543,6 +591,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -550,6 +599,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -557,6 +607,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -564,6 +615,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -571,6 +623,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -578,6 +631,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -585,6 +639,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -592,6 +647,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -599,6 +655,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -606,6 +663,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -613,6 +671,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -620,6 +679,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -627,6 +687,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -634,6 +695,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -641,6 +703,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -648,6 +711,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -655,6 +719,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -662,6 +727,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -669,6 +735,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -676,6 +743,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -683,6 +751,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -690,6 +759,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -697,6 +767,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -704,6 +775,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -711,6 +783,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -718,6 +791,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -725,6 +799,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -732,6 +807,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -739,6 +815,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -746,6 +823,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -753,6 +831,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -760,6 +839,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -767,6 +847,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -774,6 +855,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -781,6 +863,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -788,6 +871,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -795,6 +879,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -802,6 +887,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -809,6 +895,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -816,6 +903,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -823,6 +911,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -830,6 +919,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -837,6 +927,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -844,6 +935,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -851,6 +943,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -858,6 +951,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -865,6 +959,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -872,6 +967,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -879,6 +975,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -886,6 +983,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -893,6 +991,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -900,6 +999,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -907,6 +1007,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -914,6 +1015,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -921,6 +1023,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -928,6 +1031,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -935,6 +1039,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -942,6 +1047,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -949,6 +1055,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -956,6 +1063,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -963,6 +1071,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -970,6 +1079,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -977,6 +1087,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -984,6 +1095,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -991,6 +1103,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -998,6 +1111,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1005,6 +1119,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1012,6 +1127,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1019,6 +1135,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1026,6 +1143,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1033,6 +1151,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1040,6 +1159,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1047,6 +1167,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1054,6 +1175,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1061,6 +1183,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1068,6 +1191,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1075,6 +1199,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1082,6 +1207,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1089,6 +1215,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1096,6 +1223,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1103,6 +1231,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1110,6 +1239,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1117,6 +1247,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1124,6 +1255,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1136,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,6 +1277,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1152,6 +1289,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1159,6 +1297,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_existing_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1166,6 +1309,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1173,6 +1321,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1180,6 +1329,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1187,6 +1341,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1194,6 +1349,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1201,6 +1357,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1208,6 +1369,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1215,6 +1381,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1222,6 +1393,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1229,6 +1401,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1236,6 +1413,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1243,6 +1421,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1250,6 +1429,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1257,6 +1437,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1264,6 +1445,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1271,6 +1453,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1278,6 +1461,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1285,6 +1469,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1292,6 +1477,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1299,6 +1485,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1306,6 +1493,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1313,6 +1501,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1320,6 +1509,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1327,6 +1517,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1334,6 +1525,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1341,6 +1533,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1348,6 +1541,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1355,6 +1549,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1362,6 +1557,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1369,6 +1565,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1376,6 +1573,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1383,6 +1581,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1390,6 +1589,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1397,6 +1597,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1404,6 +1605,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1411,6 +1613,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1418,6 +1621,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1425,6 +1629,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1432,6 +1637,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1439,6 +1645,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1446,6 +1653,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1453,6 +1661,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1460,6 +1669,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1467,6 +1677,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1474,6 +1685,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1481,6 +1693,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1488,6 +1701,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1495,6 +1709,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1502,6 +1717,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1509,6 +1725,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1516,6 +1733,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1523,6 +1741,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1530,6 +1749,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1537,6 +1757,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1544,6 +1765,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1551,6 +1773,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1558,6 +1781,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1565,6 +1789,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1572,6 +1797,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1579,6 +1805,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1586,6 +1813,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1593,6 +1821,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1600,6 +1829,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1607,6 +1837,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1614,6 +1845,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1621,6 +1853,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1628,6 +1861,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1635,6 +1869,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1642,6 +1877,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1649,6 +1885,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1656,6 +1893,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1663,6 +1901,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1670,6 +1909,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1677,6 +1917,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1684,6 +1925,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1691,6 +1933,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1698,6 +1941,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1705,6 +1949,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1712,6 +1957,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1719,6 +1965,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1726,6 +1973,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1733,6 +1981,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1740,6 +1989,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1747,6 +1997,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1754,6 +2005,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1761,6 +2013,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1768,6 +2021,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1775,6 +2029,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1782,6 +2037,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1789,6 +2045,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1796,6 +2053,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1803,6 +2061,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1810,6 +2069,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1817,6 +2077,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1824,6 +2085,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1831,6 +2093,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1838,6 +2101,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1850,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,6 +2123,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1866,6 +2135,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1873,6 +2143,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1880,6 +2155,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1887,6 +2167,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1894,6 +2175,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1901,6 +2187,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1908,6 +2195,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1915,6 +2203,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1922,6 +2215,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1929,6 +2227,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1936,6 +2239,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1943,6 +2247,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1950,6 +2259,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1957,6 +2267,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1964,6 +2275,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1971,6 +2283,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1978,6 +2291,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1985,6 +2299,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1992,6 +2307,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1999,6 +2315,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2006,6 +2323,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2013,6 +2331,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2020,6 +2339,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2027,6 +2347,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2034,6 +2355,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2041,6 +2363,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2048,6 +2371,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2055,6 +2379,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2062,6 +2387,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2069,6 +2395,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2076,6 +2403,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2083,6 +2411,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2090,6 +2419,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2097,6 +2427,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2104,6 +2435,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2111,6 +2443,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2118,6 +2451,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2125,6 +2459,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2132,6 +2467,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2139,6 +2475,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2146,6 +2483,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2153,6 +2491,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2160,6 +2499,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2167,6 +2507,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2174,6 +2515,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2181,6 +2523,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2188,6 +2531,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2195,6 +2539,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2202,6 +2547,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2209,6 +2555,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2216,6 +2563,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2223,6 +2571,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2230,6 +2579,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2237,6 +2587,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2244,6 +2595,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2251,6 +2603,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2258,6 +2611,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2265,6 +2619,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2272,6 +2627,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2279,6 +2635,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2286,6 +2643,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2293,6 +2651,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2300,6 +2659,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2307,6 +2667,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2314,6 +2675,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2321,6 +2683,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2328,6 +2691,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2335,6 +2699,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2342,6 +2707,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2349,6 +2715,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2356,6 +2723,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2363,6 +2731,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2370,6 +2739,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2377,6 +2747,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2384,6 +2755,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2391,6 +2763,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2398,6 +2771,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2405,6 +2779,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2412,6 +2787,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2419,6 +2795,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2426,6 +2803,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2433,6 +2811,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2440,6 +2819,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2447,6 +2827,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2454,6 +2835,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2461,6 +2843,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2468,6 +2851,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2475,6 +2859,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2482,6 +2867,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2489,6 +2875,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2496,6 +2883,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2503,6 +2891,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2510,6 +2899,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2517,6 +2907,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2524,6 +2915,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2531,6 +2923,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2538,6 +2931,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2545,6 +2939,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2552,6 +2947,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2564,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2573,6 +2969,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2580,6 +2981,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2587,6 +2989,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2594,6 +3001,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2601,6 +3013,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2608,6 +3021,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2615,6 +3033,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2622,6 +3041,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2629,6 +3049,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2636,6 +3061,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2643,6 +3073,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2650,6 +3085,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2657,6 +3093,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2664,6 +3105,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2671,6 +3113,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2678,6 +3121,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2685,6 +3129,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2692,6 +3137,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2699,6 +3145,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2706,6 +3153,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2713,6 +3161,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2720,6 +3169,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2727,6 +3177,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2734,6 +3185,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2741,6 +3193,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2748,6 +3201,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2755,6 +3209,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2762,6 +3217,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2769,6 +3225,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2776,6 +3233,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2783,6 +3241,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2790,6 +3249,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2797,6 +3257,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2804,6 +3265,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2811,6 +3273,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2818,6 +3281,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2825,6 +3289,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2832,6 +3297,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2839,6 +3305,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2846,6 +3313,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2853,6 +3321,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2860,6 +3329,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2867,6 +3337,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2874,6 +3345,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2881,6 +3353,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2888,6 +3361,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2895,6 +3369,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2902,6 +3377,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2909,6 +3385,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2916,6 +3393,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2923,6 +3401,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2930,6 +3409,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2937,6 +3417,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2944,6 +3425,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2951,6 +3433,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2958,6 +3441,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2965,6 +3449,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2972,6 +3457,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2979,6 +3465,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2986,6 +3473,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2993,6 +3481,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3000,6 +3489,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3007,6 +3497,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3014,6 +3505,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3021,6 +3513,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3028,6 +3521,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3035,6 +3529,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3042,6 +3537,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3049,6 +3545,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3056,6 +3553,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3063,6 +3561,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3070,6 +3569,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3077,6 +3577,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3084,6 +3585,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3091,6 +3593,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3098,6 +3601,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3105,6 +3609,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3112,6 +3617,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3119,6 +3625,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3126,6 +3633,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3133,6 +3641,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3140,6 +3649,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3147,6 +3657,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3154,6 +3665,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3161,6 +3673,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3168,6 +3681,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3175,6 +3689,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3182,6 +3697,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3189,6 +3705,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3196,6 +3713,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3203,6 +3721,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3210,6 +3729,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3217,6 +3737,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3224,6 +3745,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3231,6 +3753,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3238,6 +3761,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3245,6 +3769,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3252,6 +3777,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3259,6 +3785,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3266,6 +3793,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3278,7 +3806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3287,6 +3815,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3294,6 +3827,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3301,6 +3835,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3308,6 +3847,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>natural_gas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3315,6 +3859,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3322,6 +3867,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3329,6 +3879,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3336,6 +3887,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3343,6 +3895,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3350,6 +3907,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3357,6 +3919,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3364,6 +3931,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3371,6 +3939,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3378,6 +3951,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3385,6 +3959,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3392,6 +3967,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3399,6 +3975,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3406,6 +3983,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3413,6 +3991,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3420,6 +3999,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3427,6 +4007,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3434,6 +4015,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3441,6 +4023,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3448,6 +4031,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3455,6 +4039,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3462,6 +4047,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3469,6 +4055,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3476,6 +4063,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3483,6 +4071,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3490,6 +4079,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3497,6 +4087,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3504,6 +4095,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3511,6 +4103,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3518,6 +4111,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3525,6 +4119,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3532,6 +4127,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3539,6 +4135,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3546,6 +4143,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3553,6 +4151,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3560,6 +4159,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3567,6 +4167,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3574,6 +4175,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3581,6 +4183,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3588,6 +4191,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3595,6 +4199,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3602,6 +4207,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3609,6 +4215,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3616,6 +4223,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3623,6 +4231,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3630,6 +4239,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3637,6 +4247,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3644,6 +4255,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3651,6 +4263,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3658,6 +4271,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3665,6 +4279,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3672,6 +4287,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3679,6 +4295,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3686,6 +4303,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3693,6 +4311,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3700,6 +4319,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3707,6 +4327,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3714,6 +4335,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3721,6 +4343,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3728,6 +4351,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3735,6 +4359,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3742,6 +4367,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3749,6 +4375,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3756,6 +4383,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3763,6 +4391,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3770,6 +4399,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3777,6 +4407,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3784,6 +4415,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3791,6 +4423,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3798,6 +4431,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3805,6 +4439,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3812,6 +4447,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3819,6 +4455,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3826,6 +4463,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3833,6 +4471,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3840,6 +4479,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3847,6 +4487,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3854,6 +4495,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3861,6 +4503,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3868,6 +4511,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3875,6 +4519,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3882,6 +4527,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3889,6 +4535,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3896,6 +4543,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3903,6 +4551,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3910,6 +4559,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3917,6 +4567,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3924,6 +4575,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3931,6 +4583,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3938,6 +4591,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3945,6 +4599,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3952,6 +4607,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3959,6 +4615,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3966,6 +4623,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3973,6 +4631,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3980,6 +4639,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3992,7 +4652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4001,6 +4661,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4008,6 +4673,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4015,6 +4681,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4022,6 +4693,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>natural_gas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4029,6 +4705,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4036,6 +4713,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4043,6 +4725,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4050,6 +4733,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4057,6 +4741,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4064,6 +4753,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4071,6 +4765,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4078,6 +4777,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4085,6 +4785,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4092,6 +4797,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4099,6 +4805,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4106,6 +4813,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4113,6 +4821,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4120,6 +4829,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4127,6 +4837,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4134,6 +4845,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4141,6 +4853,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4148,6 +4861,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4155,6 +4869,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4162,6 +4877,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4169,6 +4885,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4176,6 +4893,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4183,6 +4901,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4190,6 +4909,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4197,6 +4917,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4204,6 +4925,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4211,6 +4933,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4218,6 +4941,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4225,6 +4949,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4232,6 +4957,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4239,6 +4965,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4246,6 +4973,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4253,6 +4981,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4260,6 +4989,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4267,6 +4997,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4274,6 +5005,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4281,6 +5013,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4288,6 +5021,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4295,6 +5029,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4302,6 +5037,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4309,6 +5045,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4316,6 +5053,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4323,6 +5061,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4330,6 +5069,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4337,6 +5077,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4344,6 +5085,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4351,6 +5093,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4358,6 +5101,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4365,6 +5109,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4372,6 +5117,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4379,6 +5125,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4386,6 +5133,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4393,6 +5141,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4400,6 +5149,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4407,6 +5157,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4414,6 +5165,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4421,6 +5173,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4428,6 +5181,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4435,6 +5189,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4442,6 +5197,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4449,6 +5205,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4456,6 +5213,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4463,6 +5221,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4470,6 +5229,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4477,6 +5237,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4484,6 +5245,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4491,6 +5253,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4498,6 +5261,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4505,6 +5269,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4512,6 +5277,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4519,6 +5285,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4526,6 +5293,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4533,6 +5301,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4540,6 +5309,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4547,6 +5317,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4554,6 +5325,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4561,6 +5333,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4568,6 +5341,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4575,6 +5349,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4582,6 +5357,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4589,6 +5365,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4596,6 +5373,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4603,6 +5381,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4610,6 +5389,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4617,6 +5397,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4624,6 +5405,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4631,6 +5413,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4638,6 +5421,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4645,6 +5429,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4652,6 +5437,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4659,6 +5445,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4666,6 +5453,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4673,6 +5461,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4680,6 +5469,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4687,6 +5477,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4694,6 +5485,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4706,7 +5498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4715,6 +5507,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4722,6 +5519,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4729,6 +5527,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4736,6 +5539,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>natural_gas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4743,6 +5551,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4750,6 +5559,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4757,6 +5571,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4764,6 +5579,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4771,6 +5587,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4778,6 +5599,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4785,6 +5611,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4792,6 +5623,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4799,6 +5631,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4806,6 +5643,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4813,6 +5651,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4820,6 +5659,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4827,6 +5667,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4834,6 +5675,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4841,6 +5683,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4848,6 +5691,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4855,6 +5699,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4862,6 +5707,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4869,6 +5715,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4876,6 +5723,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4883,6 +5731,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4890,6 +5739,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4897,6 +5747,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4904,6 +5755,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4911,6 +5763,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4918,6 +5771,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4925,6 +5779,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4932,6 +5787,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4939,6 +5795,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4946,6 +5803,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4953,6 +5811,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4960,6 +5819,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4967,6 +5827,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4974,6 +5835,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4981,6 +5843,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4988,6 +5851,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4995,6 +5859,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5002,6 +5867,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5009,6 +5875,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5016,6 +5883,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5023,6 +5891,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5030,6 +5899,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5037,6 +5907,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5044,6 +5915,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5051,6 +5923,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5058,6 +5931,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5065,6 +5939,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5072,6 +5947,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5079,6 +5955,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5086,6 +5963,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5093,6 +5971,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5100,6 +5979,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5107,6 +5987,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5114,6 +5995,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5121,6 +6003,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5128,6 +6011,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5135,6 +6019,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5142,6 +6027,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5149,6 +6035,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5156,6 +6043,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5163,6 +6051,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5170,6 +6059,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5177,6 +6067,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5184,6 +6075,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5191,6 +6083,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5198,6 +6091,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5205,6 +6099,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5212,6 +6107,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5219,6 +6115,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5226,6 +6123,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5233,6 +6131,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5240,6 +6139,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5247,6 +6147,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5254,6 +6155,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5261,6 +6163,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5268,6 +6171,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5275,6 +6179,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5282,6 +6187,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5289,6 +6195,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5296,6 +6203,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5303,6 +6211,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5310,6 +6219,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5317,6 +6227,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5324,6 +6235,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5331,6 +6243,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5338,6 +6251,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5345,6 +6259,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5352,6 +6267,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5359,6 +6275,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5366,6 +6283,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5373,6 +6291,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5380,6 +6299,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5387,6 +6307,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5394,6 +6315,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5401,6 +6323,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5408,6 +6331,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5420,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5429,6 +6353,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5436,6 +6365,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5443,6 +6373,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5450,6 +6385,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5457,6 +6397,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5464,6 +6405,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5471,6 +6417,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5478,6 +6425,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5485,6 +6433,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5492,6 +6445,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5499,6 +6457,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5506,6 +6469,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5513,6 +6477,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5520,6 +6489,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5527,6 +6497,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5534,6 +6505,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5541,6 +6513,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5548,6 +6521,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5555,6 +6529,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5562,6 +6537,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5569,6 +6545,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5576,6 +6553,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5583,6 +6561,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5590,6 +6569,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5597,6 +6577,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5604,6 +6585,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5611,6 +6593,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5618,6 +6601,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5625,6 +6609,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5632,6 +6617,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5639,6 +6625,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5646,6 +6633,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5653,6 +6641,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5660,6 +6649,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5667,6 +6657,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5674,6 +6665,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5681,6 +6673,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5688,6 +6681,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5695,6 +6689,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5702,6 +6697,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5709,6 +6705,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5716,6 +6713,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5723,6 +6721,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5730,6 +6729,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5737,6 +6737,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5744,6 +6745,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5751,6 +6753,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5758,6 +6761,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5765,6 +6769,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5772,6 +6777,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5779,6 +6785,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5786,6 +6793,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5793,6 +6801,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5800,6 +6809,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5807,6 +6817,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5814,6 +6825,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5821,6 +6833,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5828,6 +6841,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5835,6 +6849,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5842,6 +6857,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5849,6 +6865,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5856,6 +6873,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5863,6 +6881,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5870,6 +6889,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5877,6 +6897,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5884,6 +6905,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5891,6 +6913,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5898,6 +6921,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5905,6 +6929,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5912,6 +6937,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5919,6 +6945,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5926,6 +6953,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5933,6 +6961,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5940,6 +6969,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5947,6 +6977,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5954,6 +6985,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5961,6 +6993,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5968,6 +7001,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5975,6 +7009,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5982,6 +7017,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5989,6 +7025,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5996,6 +7033,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6003,6 +7041,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6010,6 +7049,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6017,6 +7057,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6024,6 +7065,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6031,6 +7073,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6038,6 +7081,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6045,6 +7089,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6052,6 +7097,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6059,6 +7105,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6066,6 +7113,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6073,6 +7121,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6080,6 +7129,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6087,6 +7137,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6094,6 +7145,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6101,6 +7153,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6108,6 +7161,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6115,6 +7169,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6122,6 +7177,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6134,7 +7190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6143,6 +7199,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6150,6 +7211,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6157,6 +7219,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6164,6 +7231,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6171,6 +7243,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6178,6 +7251,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6185,6 +7263,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6192,6 +7271,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6199,6 +7279,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6206,6 +7291,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6213,6 +7303,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6220,6 +7315,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6227,6 +7323,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6234,6 +7335,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6241,6 +7343,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6248,6 +7351,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6255,6 +7359,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6262,6 +7367,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6269,6 +7375,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6276,6 +7383,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6283,6 +7391,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6290,6 +7399,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6297,6 +7407,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6304,6 +7415,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6311,6 +7423,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6318,6 +7431,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6325,6 +7439,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6332,6 +7447,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6339,6 +7455,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6346,6 +7463,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6353,6 +7471,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6360,6 +7479,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6367,6 +7487,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6374,6 +7495,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6381,6 +7503,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6388,6 +7511,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6395,6 +7519,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6402,6 +7527,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6409,6 +7535,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6416,6 +7543,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6423,6 +7551,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6430,6 +7559,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6437,6 +7567,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6444,6 +7575,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6451,6 +7583,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6458,6 +7591,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6465,6 +7599,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6472,6 +7607,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6479,6 +7615,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6486,6 +7623,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6493,6 +7631,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6500,6 +7639,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6507,6 +7647,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6514,6 +7655,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6521,6 +7663,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6528,6 +7671,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6535,6 +7679,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6542,6 +7687,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6549,6 +7695,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6556,6 +7703,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6563,6 +7711,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6570,6 +7719,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6577,6 +7727,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6584,6 +7735,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6591,6 +7743,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6598,6 +7751,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6605,6 +7759,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6612,6 +7767,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6619,6 +7775,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6626,6 +7783,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6633,6 +7791,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6640,6 +7799,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6647,6 +7807,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6654,6 +7815,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6661,6 +7823,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6668,6 +7831,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6675,6 +7839,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6682,6 +7847,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6689,6 +7855,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6696,6 +7863,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6703,6 +7871,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6710,6 +7879,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6717,6 +7887,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6724,6 +7895,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6731,6 +7903,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6738,6 +7911,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6745,6 +7919,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6752,6 +7927,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6759,6 +7935,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6766,6 +7943,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6773,6 +7951,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6780,6 +7959,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6787,6 +7967,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6794,6 +7975,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6801,6 +7983,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6808,6 +7991,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6815,6 +7999,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6822,6 +8007,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6829,6 +8015,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6836,6 +8023,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6848,7 +8036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6857,6 +8045,11 @@
           <t>Field</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6864,6 +8057,7 @@
           <t>parent_condition_name</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6871,6 +8065,11 @@
           <t>condition_name</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6878,6 +8077,11 @@
           <t>primary_fuel</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6885,6 +8089,7 @@
           <t>efficiency_description</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6892,6 +8097,11 @@
           <t>efficiency_level</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6899,6 +8109,7 @@
           <t>year_start_baseline</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6906,6 +8117,7 @@
           <t>year_end_baseline</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6913,6 +8125,11 @@
           <t>sector</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6920,6 +8137,11 @@
           <t>unit_of_characterization</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6927,6 +8149,11 @@
           <t>competition_group</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6934,6 +8161,7 @@
           <t>heating_or_cooling</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6941,6 +8169,11 @@
           <t>subgroup</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6948,6 +8181,7 @@
           <t>base_building_type</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6955,6 +8189,7 @@
           <t>interaction_group</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6962,6 +8197,7 @@
           <t>equipment_cost</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6969,6 +8205,7 @@
           <t>equipment_cost_scale_procedure</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6976,6 +8213,7 @@
           <t>labor_cost_installation</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6983,6 +8221,7 @@
           <t>effective_useful_life_yrs</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6990,6 +8229,7 @@
           <t>water_usage_gal</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6997,6 +8237,7 @@
           <t>o_and_m_costs</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7004,6 +8245,7 @@
           <t>secondary_hvac_heating_effect_flag</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7011,6 +8253,7 @@
           <t>secondary_hvac_cooling_effect_flag</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7018,6 +8261,7 @@
           <t>climate_zone_effect</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7025,6 +8269,7 @@
           <t>RET_retirement_rate</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7032,6 +8277,7 @@
           <t>RET_add_on_applicable</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7039,6 +8285,7 @@
           <t>RET_ER_applicable</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7046,6 +8293,7 @@
           <t>NC_applicable</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7053,6 +8301,7 @@
           <t>ROB_applicable</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7060,6 +8309,7 @@
           <t>RENO_applicable</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7067,6 +8317,7 @@
           <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7074,6 +8325,7 @@
           <t>fuel-end_use_combinations</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7081,6 +8333,7 @@
           <t>fuel_01_type</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7088,6 +8341,7 @@
           <t>fuel_01_consumption</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7095,6 +8349,7 @@
           <t>fuel_01_units</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7102,6 +8357,7 @@
           <t>fuel_01_end_use</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7109,6 +8365,7 @@
           <t>fuel_02_type</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7116,6 +8373,7 @@
           <t>fuel_02_consumption</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7123,6 +8381,7 @@
           <t>fuel_02_units</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7130,6 +8389,7 @@
           <t>fuel_02_end_use</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7137,6 +8397,7 @@
           <t>fuel_03_type</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7144,6 +8405,7 @@
           <t>fuel_03_consumption</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7151,6 +8413,7 @@
           <t>fuel_03_units</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7158,6 +8421,7 @@
           <t>fuel_03_end_use</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7165,6 +8429,7 @@
           <t>fuel_04_type</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7172,6 +8437,7 @@
           <t>fuel_04_consumption</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7179,6 +8445,7 @@
           <t>fuel_04_units</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7186,6 +8453,7 @@
           <t>fuel_04_end_use</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7193,6 +8461,7 @@
           <t>fuel_05_type</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7200,6 +8469,7 @@
           <t>fuel_05_consumption</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7207,6 +8477,7 @@
           <t>fuel_05_units</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7214,6 +8485,7 @@
           <t>fuel_05_end_use</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7221,6 +8493,7 @@
           <t>fuel_06_type</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7228,6 +8501,7 @@
           <t>fuel_06_consumption</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7235,6 +8509,7 @@
           <t>fuel_06_units</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7242,6 +8517,7 @@
           <t>fuel_06_end_use</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7249,6 +8525,7 @@
           <t>fuel_07_type</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7256,6 +8533,7 @@
           <t>fuel_07_consumption</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7263,6 +8541,7 @@
           <t>fuel_07_units</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7270,6 +8549,7 @@
           <t>fuel_07_end_use</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7277,6 +8557,7 @@
           <t>fuel_08_type</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7284,6 +8565,7 @@
           <t>fuel_08_consumption</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7291,6 +8573,7 @@
           <t>fuel_08_units</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7298,6 +8581,7 @@
           <t>fuel_08_end_use</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7305,6 +8589,7 @@
           <t>fuel_09_type</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7312,6 +8597,7 @@
           <t>fuel_09_consumption</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7319,6 +8605,7 @@
           <t>fuel_09_units</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7326,6 +8613,7 @@
           <t>fuel_09_end_use</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7333,6 +8621,7 @@
           <t>fuel_10_type</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7340,6 +8629,7 @@
           <t>fuel_10_consumption</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7347,6 +8637,7 @@
           <t>fuel_10_units</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7354,6 +8645,7 @@
           <t>fuel_10_end_use</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7361,6 +8653,7 @@
           <t>fuel_11_type</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7368,6 +8661,7 @@
           <t>fuel_11_consumption</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7375,6 +8669,7 @@
           <t>fuel_11_units</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7382,6 +8677,7 @@
           <t>fuel_11_end_use</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7389,6 +8685,7 @@
           <t>fuel_12_type</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7396,6 +8693,7 @@
           <t>fuel_12_consumption</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7403,6 +8701,7 @@
           <t>fuel_12_units</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7410,6 +8709,7 @@
           <t>fuel_12_end_use</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7417,6 +8717,7 @@
           <t>fuel_13_type</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7424,6 +8725,7 @@
           <t>fuel_13_consumption</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7431,6 +8733,7 @@
           <t>fuel_13_units</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7438,6 +8741,7 @@
           <t>fuel_13_end_use</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7445,6 +8749,7 @@
           <t>fuel_14_type</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7452,6 +8757,7 @@
           <t>fuel_14_consumption</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7459,6 +8765,7 @@
           <t>fuel_14_units</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7466,6 +8773,7 @@
           <t>fuel_14_end_use</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7473,6 +8781,7 @@
           <t>fuel_15_type</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7480,6 +8789,7 @@
           <t>fuel_15_consumption</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7487,6 +8797,7 @@
           <t>fuel_15_units</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7494,6 +8805,7 @@
           <t>fuel_15_end_use</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7501,6 +8813,7 @@
           <t>fuel_16_type</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7508,6 +8821,7 @@
           <t>fuel_16_consumption</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7515,6 +8829,7 @@
           <t>fuel_16_units</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7522,6 +8837,7 @@
           <t>fuel_16_end_use</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7529,6 +8845,7 @@
           <t>fuel_17_type</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7536,6 +8853,7 @@
           <t>fuel_17_consumption</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7543,6 +8861,7 @@
           <t>fuel_17_units</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7550,6 +8869,7 @@
           <t>fuel_17_end_use</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -7,16 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_efficient_residential" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_baseline_residential" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_existing_residential" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_efficient_residential" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_baseline_residential" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_existing_residential" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_efficient_residential" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_baseline_residential" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_top10_residential" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_existing_residential" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_efficient_residenti" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_baseline_residentia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_existing_residentia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_efficient_r" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_baseline_re" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_existing_re" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_efficient" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_baseline_" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_top10_res" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_existing_" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -644,7 +648,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -700,7 +704,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -708,7 +712,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1258,6 +1262,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1289,7 +1559,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1490,7 +1764,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1546,7 +1820,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1554,7 +1828,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2104,6 +2378,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2135,7 +2675,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2336,7 +2880,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -2392,7 +2936,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2400,7 +2944,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2950,6 +3494,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2981,7 +3791,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3182,7 +3996,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -3238,7 +4052,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -3246,7 +4060,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -3796,6 +4610,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3827,7 +4907,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4028,7 +5112,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -4084,7 +5168,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -4092,7 +5176,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -4642,6 +5726,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4673,7 +6023,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4874,7 +6228,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -4930,7 +6284,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -4938,7 +6292,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -5488,6 +6842,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5519,7 +7139,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5720,7 +7344,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -5776,7 +7400,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -5784,7 +7408,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -6334,6 +7958,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6365,7 +8255,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6566,7 +8460,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -6622,7 +8516,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -6630,7 +8524,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -7180,6 +9074,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7211,7 +9371,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7412,7 +9576,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -7468,7 +9632,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -7476,7 +9640,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -8026,6 +10190,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8057,7 +10487,11 @@
           <t>parent_condition_name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8258,7 +10692,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>climate_zone_effect</t>
+          <t>climate_zone</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -8314,7 +10748,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>equipment_savings_scale_procedure</t>
+          <t>DEMO_applicable</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -8322,7 +10756,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fuel-end_use_combinations</t>
+          <t>equipment_savings_scale_procedure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -8872,6 +11306,272 @@
       <c r="B100" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -7,16 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_efficient_residenti" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_baseline_residentia" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_oil_existing_residentia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_efficient_r" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_baseline_re" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="furnace_natural_gas_existing_re" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_efficient" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_baseline_" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_top10_res" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_existing_" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_furnace_oil_efficient_residen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_furnace_oil_baseline_resident" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_furnace_oil_existing_resident" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_furnace_oil_efficient_residen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_furnace_oil_baseline_resident" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_furnace_oil_existing_resident" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_furnace_natural_gas_efficient" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_furnace_natural_gas_baseline_" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_furnace_natural_gas_existing_" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_furnace_natural_gas_efficient" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_furnace_natural_gas_baseline_" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_furnace_natural_gas_existing_" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_efficient" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_baseline_" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_top10_res" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="refrigerator_electric_existing_" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
@@ -651,7 +657,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1297,7 +1307,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -1561,7 +1571,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>refrigerator</t>
+          <t>furnace</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>refrigerator_electric_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1595,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>natural_gas</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1615,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1667,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1687,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1777,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2413,7 +2427,6711 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parent_condition_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>condition_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_fuel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>natural_gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>efficiency_description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_start_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>year_end_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unit_of_characterization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_or_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base_building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>interaction_group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equipment_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>equipment_cost_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>labor_cost_installation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effective_useful_life_yrs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_usage_gal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>o_and_m_costs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>secondary_hvac_heating_effect_flag</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>secondary_hvac_cooling_effect_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate_zone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RET_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RET_add_on_applicable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RET_ER_applicable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NC_applicable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ROB_applicable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RENO_applicable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEMO_applicable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>equipment_savings_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fuel_01_type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fuel_01_consumption</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fuel_01_units</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fuel_01_end_use</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fuel_02_type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fuel_02_consumption</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fuel_02_units</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fuel_02_end_use</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fuel_03_type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fuel_03_consumption</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fuel_03_units</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fuel_03_end_use</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fuel_04_type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fuel_04_consumption</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel_04_units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fuel_04_end_use</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fuel_05_type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fuel_05_consumption</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fuel_05_units</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fuel_05_end_use</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fuel_06_type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fuel_06_consumption</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fuel_06_units</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fuel_06_end_use</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fuel_07_type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fuel_07_consumption</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fuel_07_units</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fuel_07_end_use</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fuel_08_type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fuel_08_consumption</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fuel_08_units</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fuel_08_end_use</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fuel_09_type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fuel_09_consumption</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fuel_09_units</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fuel_09_end_use</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fuel_10_type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fuel_10_consumption</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fuel_10_units</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fuel_10_end_use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fuel_11_type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fuel_11_consumption</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuel_11_units</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fuel_11_end_use</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fuel_12_type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fuel_12_consumption</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fuel_12_units</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fuel_12_end_use</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuel_13_type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuel_13_consumption</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fuel_13_units</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fuel_13_end_use</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fuel_14_type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fuel_14_consumption</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fuel_14_units</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fuel_14_end_use</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fuel_15_type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fuel_15_consumption</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fuel_15_units</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fuel_15_end_use</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fuel_16_type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fuel_16_consumption</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fuel_16_units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fuel_16_end_use</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>fuel_17_type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>fuel_17_consumption</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>fuel_17_units</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>fuel_17_end_use</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parent_condition_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>condition_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_fuel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>natural_gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>efficiency_description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_start_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>year_end_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unit_of_characterization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_or_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base_building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>interaction_group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equipment_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>equipment_cost_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>labor_cost_installation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effective_useful_life_yrs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_usage_gal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>o_and_m_costs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>secondary_hvac_heating_effect_flag</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>secondary_hvac_cooling_effect_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate_zone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RET_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RET_add_on_applicable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RET_ER_applicable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NC_applicable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ROB_applicable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RENO_applicable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEMO_applicable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>equipment_savings_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fuel_01_type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fuel_01_consumption</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fuel_01_units</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fuel_01_end_use</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fuel_02_type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fuel_02_consumption</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fuel_02_units</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fuel_02_end_use</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fuel_03_type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fuel_03_consumption</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fuel_03_units</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fuel_03_end_use</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fuel_04_type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fuel_04_consumption</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel_04_units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fuel_04_end_use</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fuel_05_type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fuel_05_consumption</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fuel_05_units</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fuel_05_end_use</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fuel_06_type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fuel_06_consumption</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fuel_06_units</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fuel_06_end_use</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fuel_07_type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fuel_07_consumption</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fuel_07_units</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fuel_07_end_use</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fuel_08_type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fuel_08_consumption</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fuel_08_units</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fuel_08_end_use</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fuel_09_type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fuel_09_consumption</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fuel_09_units</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fuel_09_end_use</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fuel_10_type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fuel_10_consumption</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fuel_10_units</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fuel_10_end_use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fuel_11_type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fuel_11_consumption</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuel_11_units</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fuel_11_end_use</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fuel_12_type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fuel_12_consumption</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fuel_12_units</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fuel_12_end_use</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuel_13_type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuel_13_consumption</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fuel_13_units</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fuel_13_end_use</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fuel_14_type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fuel_14_consumption</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fuel_14_units</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fuel_14_end_use</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fuel_15_type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fuel_15_consumption</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fuel_15_units</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fuel_15_end_use</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fuel_16_type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fuel_16_consumption</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fuel_16_units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fuel_16_end_use</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>fuel_17_type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>fuel_17_consumption</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>fuel_17_units</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>fuel_17_end_use</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parent_condition_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>condition_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_fuel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>efficiency_description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_start_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>year_end_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unit_of_characterization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_or_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base_building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>interaction_group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equipment_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>equipment_cost_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>labor_cost_installation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effective_useful_life_yrs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_usage_gal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>o_and_m_costs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>secondary_hvac_heating_effect_flag</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>secondary_hvac_cooling_effect_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate_zone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RET_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RET_add_on_applicable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RET_ER_applicable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NC_applicable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ROB_applicable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RENO_applicable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEMO_applicable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>equipment_savings_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fuel_01_type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fuel_01_consumption</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fuel_01_units</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fuel_01_end_use</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fuel_02_type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fuel_02_consumption</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fuel_02_units</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fuel_02_end_use</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fuel_03_type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fuel_03_consumption</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fuel_03_units</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fuel_03_end_use</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fuel_04_type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fuel_04_consumption</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel_04_units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fuel_04_end_use</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fuel_05_type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fuel_05_consumption</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fuel_05_units</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fuel_05_end_use</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fuel_06_type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fuel_06_consumption</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fuel_06_units</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fuel_06_end_use</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fuel_07_type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fuel_07_consumption</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fuel_07_units</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fuel_07_end_use</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fuel_08_type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fuel_08_consumption</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fuel_08_units</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fuel_08_end_use</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fuel_09_type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fuel_09_consumption</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fuel_09_units</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fuel_09_end_use</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fuel_10_type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fuel_10_consumption</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fuel_10_units</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fuel_10_end_use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fuel_11_type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fuel_11_consumption</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuel_11_units</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fuel_11_end_use</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fuel_12_type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fuel_12_consumption</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fuel_12_units</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fuel_12_end_use</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuel_13_type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuel_13_consumption</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fuel_13_units</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fuel_13_end_use</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fuel_14_type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fuel_14_consumption</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fuel_14_units</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fuel_14_end_use</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fuel_15_type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fuel_15_consumption</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fuel_15_units</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fuel_15_end_use</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fuel_16_type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fuel_16_consumption</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fuel_16_units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fuel_16_end_use</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>fuel_17_type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>fuel_17_consumption</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>fuel_17_units</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>fuel_17_end_use</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parent_condition_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>condition_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_fuel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>efficiency_description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_start_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>year_end_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unit_of_characterization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_or_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base_building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>interaction_group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equipment_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>equipment_cost_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>labor_cost_installation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effective_useful_life_yrs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_usage_gal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>o_and_m_costs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>secondary_hvac_heating_effect_flag</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>secondary_hvac_cooling_effect_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate_zone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RET_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RET_add_on_applicable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RET_ER_applicable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NC_applicable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ROB_applicable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RENO_applicable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEMO_applicable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>equipment_savings_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fuel_01_type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fuel_01_consumption</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fuel_01_units</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fuel_01_end_use</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fuel_02_type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fuel_02_consumption</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fuel_02_units</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fuel_02_end_use</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fuel_03_type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fuel_03_consumption</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fuel_03_units</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fuel_03_end_use</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fuel_04_type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fuel_04_consumption</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel_04_units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fuel_04_end_use</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fuel_05_type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fuel_05_consumption</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fuel_05_units</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fuel_05_end_use</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fuel_06_type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fuel_06_consumption</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fuel_06_units</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fuel_06_end_use</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fuel_07_type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fuel_07_consumption</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fuel_07_units</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fuel_07_end_use</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fuel_08_type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fuel_08_consumption</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fuel_08_units</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fuel_08_end_use</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fuel_09_type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fuel_09_consumption</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fuel_09_units</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fuel_09_end_use</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fuel_10_type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fuel_10_consumption</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fuel_10_units</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fuel_10_end_use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fuel_11_type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fuel_11_consumption</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuel_11_units</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fuel_11_end_use</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fuel_12_type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fuel_12_consumption</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fuel_12_units</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fuel_12_end_use</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuel_13_type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuel_13_consumption</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fuel_13_units</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fuel_13_end_use</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fuel_14_type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fuel_14_consumption</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fuel_14_units</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fuel_14_end_use</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fuel_15_type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fuel_15_consumption</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fuel_15_units</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fuel_15_end_use</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fuel_16_type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fuel_16_consumption</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fuel_16_units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fuel_16_end_use</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>fuel_17_type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>fuel_17_consumption</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>fuel_17_units</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>fuel_17_end_use</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parent_condition_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>condition_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_fuel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>efficiency_description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_start_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>year_end_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unit_of_characterization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_or_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base_building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>interaction_group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equipment_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>equipment_cost_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>labor_cost_installation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effective_useful_life_yrs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_usage_gal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>o_and_m_costs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>secondary_hvac_heating_effect_flag</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>secondary_hvac_cooling_effect_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate_zone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RET_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RET_add_on_applicable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RET_ER_applicable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NC_applicable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ROB_applicable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RENO_applicable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEMO_applicable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>equipment_savings_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fuel_01_type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fuel_01_consumption</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fuel_01_units</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fuel_01_end_use</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fuel_02_type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fuel_02_consumption</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fuel_02_units</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fuel_02_end_use</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fuel_03_type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fuel_03_consumption</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fuel_03_units</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fuel_03_end_use</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fuel_04_type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fuel_04_consumption</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel_04_units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fuel_04_end_use</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fuel_05_type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fuel_05_consumption</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fuel_05_units</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fuel_05_end_use</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fuel_06_type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fuel_06_consumption</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fuel_06_units</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fuel_06_end_use</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fuel_07_type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fuel_07_consumption</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fuel_07_units</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fuel_07_end_use</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fuel_08_type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fuel_08_consumption</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fuel_08_units</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fuel_08_end_use</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fuel_09_type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fuel_09_consumption</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fuel_09_units</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fuel_09_end_use</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fuel_10_type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fuel_10_consumption</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fuel_10_units</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fuel_10_end_use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fuel_11_type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fuel_11_consumption</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuel_11_units</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fuel_11_end_use</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fuel_12_type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fuel_12_consumption</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fuel_12_units</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fuel_12_end_use</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuel_13_type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuel_13_consumption</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fuel_13_units</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fuel_13_end_use</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fuel_14_type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fuel_14_consumption</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fuel_14_units</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fuel_14_end_use</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fuel_15_type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fuel_15_consumption</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fuel_15_units</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fuel_15_end_use</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fuel_16_type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fuel_16_consumption</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fuel_16_units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fuel_16_end_use</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>fuel_17_type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>fuel_17_consumption</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>fuel_17_units</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>fuel_17_end_use</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"electric,gas,propane,fuel_oil"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kwh,mmbtu,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"appliance,motors,heating,cooling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>parent_condition_name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>condition_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_existing_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_fuel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>efficiency_description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>year_start_baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>year_end_baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>unit_of_characterization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_or_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>base_building_type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>interaction_group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equipment_cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>equipment_cost_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>labor_cost_installation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effective_useful_life_yrs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_usage_gal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>o_and_m_costs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>secondary_hvac_heating_effect_flag</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>secondary_hvac_cooling_effect_flag</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>climate_zone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RET_retirement_rate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RET_add_on_applicable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RET_ER_applicable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NC_applicable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ROB_applicable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RENO_applicable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEMO_applicable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>equipment_savings_scale_procedure</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fuel_01_type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fuel_01_consumption</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fuel_01_units</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fuel_01_end_use</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fuel_02_type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fuel_02_consumption</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fuel_02_units</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fuel_02_end_use</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fuel_03_type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fuel_03_consumption</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fuel_03_units</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fuel_03_end_use</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fuel_04_type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fuel_04_consumption</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fuel_04_units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fuel_04_end_use</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fuel_05_type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fuel_05_consumption</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fuel_05_units</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fuel_05_end_use</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fuel_06_type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fuel_06_consumption</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fuel_06_units</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fuel_06_end_use</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fuel_07_type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fuel_07_consumption</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fuel_07_units</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fuel_07_end_use</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fuel_08_type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fuel_08_consumption</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fuel_08_units</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fuel_08_end_use</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fuel_09_type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fuel_09_consumption</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fuel_09_units</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fuel_09_end_use</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fuel_10_type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fuel_10_consumption</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fuel_10_units</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fuel_10_end_use</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fuel_11_type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fuel_11_consumption</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuel_11_units</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fuel_11_end_use</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fuel_12_type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fuel_12_consumption</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fuel_12_units</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fuel_12_end_use</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fuel_13_type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fuel_13_consumption</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fuel_13_units</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fuel_13_end_use</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fuel_14_type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fuel_14_consumption</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>fuel_14_units</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>fuel_14_end_use</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fuel_15_type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fuel_15_consumption</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fuel_15_units</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fuel_15_end_use</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>fuel_16_type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>fuel_16_consumption</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>fuel_16_units</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>fuel_16_end_use</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>fuel_17_type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>fuel_17_consumption</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>fuel_17_units</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>fuel_17_end_use</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="88">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"heating,cooling,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"test,test_2,nan"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Standard,Manual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>-999999999</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -2689,7 +9407,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
@@ -2883,7 +9601,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3529,7 +10251,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -3805,7 +10527,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
@@ -3999,7 +10721,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4645,7 +11371,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -4921,7 +11647,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
@@ -4933,7 +11659,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>oil</t>
         </is>
       </c>
     </row>
@@ -5025,7 +11751,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
     </row>
@@ -5115,7 +11841,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5761,7 +12491,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -6037,7 +12767,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
@@ -6049,7 +12779,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>oil</t>
         </is>
       </c>
     </row>
@@ -6141,7 +12871,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
     </row>
@@ -6231,7 +12961,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6877,7 +13611,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -7153,7 +13887,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
@@ -7165,7 +13899,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>oil</t>
         </is>
       </c>
     </row>
@@ -7257,7 +13991,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
     </row>
@@ -7347,7 +14081,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7993,7 +14731,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -8257,7 +14995,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>refrigerator</t>
+          <t>furnace</t>
         </is>
       </c>
     </row>
@@ -8269,7 +15007,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
@@ -8281,7 +15019,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>natural_gas</t>
         </is>
       </c>
     </row>
@@ -8353,7 +15091,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
     </row>
@@ -8373,7 +15111,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
     </row>
@@ -8463,7 +15201,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9109,7 +15851,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -9373,7 +16115,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>refrigerator</t>
+          <t>furnace</t>
         </is>
       </c>
     </row>
@@ -9385,7 +16127,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
@@ -9397,7 +16139,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>natural_gas</t>
         </is>
       </c>
     </row>
@@ -9469,7 +16211,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
     </row>
@@ -9489,7 +16231,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
     </row>
@@ -9579,7 +16321,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10225,7 +16971,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>
@@ -10489,7 +17235,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>refrigerator</t>
+          <t>furnace</t>
         </is>
       </c>
     </row>
@@ -10501,7 +17247,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
@@ -10513,7 +17259,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>natural_gas</t>
         </is>
       </c>
     </row>
@@ -10533,7 +17279,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -10585,7 +17331,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
     </row>
@@ -10605,7 +17351,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
     </row>
@@ -10695,7 +17441,11 @@
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11341,7 +18091,7 @@
       <formula1>-999999999</formula1>
     </dataValidation>
     <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1"</formula1>
+      <formula1>"1,2"</formula1>
     </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Input" error="Please enter a numeric value" type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>-999999999</formula1>

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,6 +1270,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -1548,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2390,6 +2398,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -2668,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3510,6 +3526,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -3788,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4630,6 +4654,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -4908,7 +4940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5746,6 +5778,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -6024,7 +6064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6862,6 +6902,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -7140,7 +7188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7978,6 +8026,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -8256,7 +8312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9094,6 +9150,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -9372,7 +9436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10214,6 +10278,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -10492,7 +10564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11334,6 +11406,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -11612,7 +11692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12454,6 +12534,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -12732,7 +12820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13574,6 +13662,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -13852,7 +13948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14694,6 +14790,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -14972,7 +15076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15814,6 +15918,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -16092,7 +16204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16934,6 +17046,14 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="88">
@@ -17212,7 +17332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18055,6 +18175,14 @@
       </c>
       <c r="B100" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="88">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -502,7 +502,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1280,13 +1280,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -1630,7 +1624,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -1638,7 +1632,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -2408,13 +2402,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -2758,7 +2746,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -2766,7 +2754,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -3536,13 +3524,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -3886,7 +3868,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -3894,7 +3876,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -4664,13 +4646,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -5014,7 +4990,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -5022,7 +4998,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -5788,13 +5764,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -6138,7 +6108,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -6146,7 +6116,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -6912,13 +6882,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -7262,7 +7226,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -7270,7 +7234,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -8036,13 +8000,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -8386,7 +8344,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -8394,7 +8352,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -9160,13 +9118,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -9510,7 +9462,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -9518,7 +9470,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -10288,13 +10240,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -10638,7 +10584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -10646,7 +10592,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11416,13 +11362,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -11766,7 +11706,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11774,7 +11714,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -12544,13 +12484,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -12894,7 +12828,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -12902,7 +12836,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -13672,13 +13606,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -14022,7 +13950,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -14030,7 +13958,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -14800,13 +14728,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -15150,7 +15072,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -15158,7 +15080,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -15928,13 +15850,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -16278,7 +16194,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -16286,7 +16202,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -17056,13 +16972,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
@@ -17406,7 +17316,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>year_start_baseline</t>
+          <t>year_start_baseline_shift</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -17414,7 +17324,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>year_end_baseline</t>
+          <t>year_end_baseline_shift</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -18184,13 +18094,7 @@
       <c r="B101" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="88">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"2026,2027,2028,2029,2030,2031,2032,2033,2034,2035,2036,2037,2038,2039,2040,2041,2042,2043,2044,2045"</formula1>
-    </dataValidation>
+  <dataValidations count="86">
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="11_AB8F638C6A60A89395C7D8944AA769367E53E299" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FE2FF8E-C7B2-489E-82DE-251A32453FF5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_196CAD87845F77693373F1A1838BFA64C93207B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_furnace_oil_efficient_residen" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="146">
   <si>
     <t>Field</t>
   </si>
@@ -367,6 +367,42 @@
     <t>reference</t>
   </si>
   <si>
+    <t>nlirnc_applicable</t>
+  </si>
+  <si>
+    <t>nlirrepl_applicable</t>
+  </si>
+  <si>
+    <t>nlirret_applicable</t>
+  </si>
+  <si>
+    <t>lirnc_applicable</t>
+  </si>
+  <si>
+    <t>lirrepl_applicable</t>
+  </si>
+  <si>
+    <t>lirret_applicable</t>
+  </si>
+  <si>
+    <t>scinc_applicable</t>
+  </si>
+  <si>
+    <t>scirepl_applicable</t>
+  </si>
+  <si>
+    <t>sciret_applicable</t>
+  </si>
+  <si>
+    <t>lcinc_applicable</t>
+  </si>
+  <si>
+    <t>lcirepl_applicable</t>
+  </si>
+  <si>
+    <t>lciret_applicable</t>
+  </si>
+  <si>
     <t>furnace_oil_baseline_residential_1</t>
   </si>
   <si>
@@ -436,55 +472,7 @@
     <t>refrigerator_electric_top10_residential</t>
   </si>
   <si>
-    <t>efficient</t>
-  </si>
-  <si>
-    <t>heating</t>
-  </si>
-  <si>
-    <t>single_family</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>fuel_oil</t>
-  </si>
-  <si>
-    <t>mmbtu</t>
-  </si>
-  <si>
-    <t>kwh</t>
-  </si>
-  <si>
-    <t>baseline</t>
-  </si>
-  <si>
-    <t>existing</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>nan</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>appliance</t>
-  </si>
-  <si>
-    <t>Baseline</t>
+    <t>refrigerator_electric_existing_residential</t>
   </si>
 </sst>
 </file>
@@ -824,11 +812,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="45.42578125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -866,9 +851,6 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -882,17 +864,11 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -922,9 +898,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -938,81 +911,51 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>1000</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -1026,166 +969,118 @@
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -1453,6 +1348,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1433,7 @@
     <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0000-000012000000}">
@@ -1497,11 +1452,8 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="39.5703125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1524,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1532,16 +1484,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1555,17 +1504,11 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>250</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1595,270 +1538,189 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>1000</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2128,39 +1990,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{29586D98-44D9-4F5E-BD59-EC8D2039A5CD}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0900-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{9D250121-12E9-47A1-A7C4-F7BDEDEFE45A}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0900-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{33997DAF-3C14-40FD-9017-B12997A8DF75}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0900-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{4B67D82B-9886-4657-A437-8D98142507AF}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0900-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{1ED24E09-9AC8-438F-9D60-692C1FBFC78C}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0900-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{B9EE2B97-7BE7-43DC-9DBF-1661CFCF5DE7}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0900-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{E07E1C89-F05B-4A4E-A177-EB0BD1258072}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0900-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{B5D42FC5-3CBD-47FD-880C-26BE17FE2F34}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0900-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{899D521D-3E22-49B7-9B6A-CA184C7B54FE}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0900-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{B501853B-5AC8-4BEA-A0A4-C8BF29F900C6}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0900-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{53DF13CD-6388-4DA3-B214-A3A19A1C1ED1}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0900-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2170,11 +2092,8 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="39.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2197,7 +2116,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2205,40 +2124,31 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -2274,261 +2184,183 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>900</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2798,39 +2630,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{FEE24731-9952-4002-8C18-5C1E9AAD3911}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{1A90428E-D7FB-4A23-AD63-BD6B0912DFE8}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0A00-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{08FF5B75-7419-47C9-9D5A-F52F0633825C}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0A00-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B34 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B16 B25 B20:B21 B18" xr:uid="{B154B723-ED44-4DBB-B2D6-84B0AF4AB73E}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0A00-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{041974CF-0B1B-4215-988F-29696F239D2D}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0A00-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{3AC5AC76-3A81-4F14-9D28-E4371215DF6A}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0A00-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{D2A2E1A6-8723-4D20-88DB-F857149E68B7}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0A00-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{5F7845CE-05B2-49AD-B40B-155021430E19}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0A00-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{483A626E-5A98-4569-BF17-7A67F9B48DBD}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0A00-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{D7616C41-9F6F-4832-8D03-6449B060D371}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0A00-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{B2821C4C-B4F2-432A-87FC-30DCD4265F28}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0A00-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2840,11 +2732,8 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2867,7 +2756,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2875,40 +2764,31 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -2938,270 +2818,189 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>750</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3471,39 +3270,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{96D2CF7D-168B-47E2-9720-26DB585A9DC7}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0B00-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{DEEBCF6B-682A-4645-87CA-17ECE14CF377}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0B00-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{D27568A1-4D32-4174-A30A-4D6031EB4B36}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0B00-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B34 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B16 B25 B20:B21 B18" xr:uid="{D608C9D1-0C76-4159-859F-A0D5B8FF375D}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0B00-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{072FB253-59F4-449A-98D3-AEE40FAFE255}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0B00-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{FA8893C6-70B6-4A27-AAF1-11AD59D92F59}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0B00-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{EAC2BB22-6ABC-464A-8CA1-693F20DB124C}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0B00-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{26FAED63-000F-47ED-AC81-14B2B38B9054}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0B00-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{C8ABC339-D7E0-4751-A642-598CC196176E}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0B00-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{8D8417CA-3970-41DE-9CC8-4B5F07649E49}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0B00-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{F3361D88-3F52-4FB1-AD8B-326BB2C0E452}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0B00-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3513,11 +3372,8 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -3532,7 +3388,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3540,7 +3396,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3548,16 +3404,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -3598,7 +3451,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3611,240 +3464,180 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -4112,6 +3905,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4137,7 +3990,7 @@
     <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0C00-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{00000000-0002-0000-0C00-00000B000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0C00-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0C00-000012000000}">
@@ -4156,11 +4009,8 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4175,7 +4025,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4183,7 +4033,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4191,23 +4041,20 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>0</v>
+      <c r="B6" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4241,7 +4088,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4254,240 +4101,180 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -4757,39 +4544,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{F6BFA5D3-05D8-4C18-BD43-5784F3BC9357}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0D00-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{21C4C0AB-1700-4384-A553-966349C7AA32}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0D00-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{23E39788-26B7-42CC-A3FA-65945DAC9E61}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0D00-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B70 B98 B94 B90 B86 B82 B78 B74 B16 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0D00-000003000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0D00-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{3CA5B7FA-8EED-4CDB-A0A0-28D577102A7F}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0D00-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{C5168641-05FA-403B-B651-297EE92197E9}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0D00-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{0DB2B1A1-6630-4CC9-B76D-D7EF0E593EF3}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0D00-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{9FECB4FC-2AB8-49D4-A05F-3E372FC811E9}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0D00-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B69 B97 B93 B89 B85 B81 B77 B73 B33 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0D00-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0D00-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B71 B99 B95 B91 B87 B83 B79 B75 B35 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0D00-000014000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0D00-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B68 B100 B96 B92 B88 B84 B80 B76 B72 B36 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0D00-000015000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0D00-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4799,11 +4646,8 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="35.42578125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4818,7 +4662,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4826,7 +4670,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4834,7 +4678,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4847,7 +4691,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4881,7 +4725,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4894,240 +4738,180 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -5397,39 +5181,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{3D568B34-72DA-4D49-889E-2BE26F16CDBD}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0E00-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{BC401BCB-4033-4BEC-AD75-3C299E4AB125}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0E00-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{D6A95705-1D50-4FB9-8440-2AB0377D8C00}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0E00-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B46 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B16 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0E00-000003000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0E00-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{7BF57276-E96C-4F77-A8AD-41443CC1FA92}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0E00-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{B4067E2D-DE67-49B3-AEED-789272E692DE}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0E00-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{99854005-6422-4CCC-83FC-2732BBED739E}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0E00-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{1463B847-7606-4E7B-B015-7F4E54F0271B}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0E00-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B45 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B33 B41 B37" xr:uid="{00000000-0002-0000-0E00-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0E00-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B47 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B35 B43 B39" xr:uid="{00000000-0002-0000-0E00-000014000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0E00-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B44 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B36 B40" xr:uid="{00000000-0002-0000-0E00-000015000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0E00-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5439,7 +5283,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5455,7 +5299,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5463,7 +5307,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5471,7 +5315,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5484,7 +5328,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5518,7 +5362,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5531,240 +5375,180 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -6034,39 +5818,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{353CA4FC-1AFF-4FB9-8723-43CDF20D27D6}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0F00-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{B158D7EE-94BD-4BA7-9985-2C7F209A8EBA}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0F00-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{E38D20E7-C587-4623-9ACF-4A82CBCD21D8}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0F00-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B46 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B16 B42 B38 B34 B25 B20:B21 B18" xr:uid="{9DEA3C41-FA83-4AB5-83AC-5BDF19874DF6}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0F00-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{7FD76440-7FF0-45B8-9C06-36D0A76FD147}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0F00-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{26C2C16E-2C47-48BF-BD22-E42CE3FF5490}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0F00-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{70C8E6B3-22F1-4EBF-B935-F7C64E25A63F}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0F00-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{212F7EBB-C38A-4A86-8C06-9FEC23E89B2B}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0F00-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B45 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B33 B41 B37" xr:uid="{DF23F97D-54D8-45AD-9C60-D530A4CB4043}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0F00-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B47 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B35 B43 B39" xr:uid="{F7A4515C-1CE2-4447-A68C-2FC83FD390F8}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0F00-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B44 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B36 B40" xr:uid="{5E7F53E1-C4E1-48B5-B776-77866BBA3A3F}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0F00-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6076,12 +5920,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="35.140625" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -6104,7 +5944,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6119,33 +5959,24 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -6175,9 +6006,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -6191,81 +6019,51 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>900</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -6279,166 +6077,118 @@
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -6706,6 +6456,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6713,34 +6523,34 @@
     <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{612DEF7C-AB32-4CB7-A896-B2209BFC6B68}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{F0B298CA-9F59-4119-9529-25220537B451}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B42 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B16 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{A0AF2D60-CC09-4511-AD06-D157484403E5}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{565687FC-B9FD-463E-AC6C-B0D578CC1FEE}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{C9EA01EF-B578-4D70-8D16-D58213DD9A91}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0100-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{09F43414-4DC0-4F2A-AC8A-5358854F4F63}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0100-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B41 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B33 B37" xr:uid="{00000000-0002-0000-0100-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0100-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B43 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B35 B39" xr:uid="{00000000-0002-0000-0100-000014000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0100-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B44 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B36 B40" xr:uid="{00000000-0002-0000-0100-000015000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0100-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6750,11 +6560,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -6777,7 +6584,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6792,33 +6599,24 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -6848,9 +6646,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -6864,81 +6659,51 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>800</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -6952,166 +6717,118 @@
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -7379,6 +7096,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -7386,34 +7163,34 @@
     <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{0F83D97D-1E3D-432B-80A4-C625EC6058BC}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{13A2CD41-D7E2-4548-AC00-F8EEA63D82E7}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B42 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B16 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{618025D6-A1AA-45BD-9A28-53527AC3D0B2}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{58FCE76B-187D-458C-B80F-5AE2D9711AE7}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0200-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{489F0254-BB70-444D-ADD5-8639ED21F2D7}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0200-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{29BE7328-D01C-447F-B63B-7ACCC314AE84}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0200-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B41 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B33 B37" xr:uid="{00000000-0002-0000-0200-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0200-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B43 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B35 B39" xr:uid="{00000000-0002-0000-0200-000014000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0200-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B44 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B36 B40" xr:uid="{00000000-0002-0000-0200-000015000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0200-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7423,11 +7200,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="37.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -7450,7 +7224,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7465,9 +7239,6 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -7481,17 +7252,11 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -7521,9 +7286,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -7537,254 +7299,176 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>1000</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -8054,39 +7738,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{5AC20B07-8A4B-4A2C-9D5A-A0C5B3CB9E51}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{31F3737E-498D-4394-AD0C-98C7615D1FED}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{FA4774B3-0795-43DD-B4D9-C9E582C37C88}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{B6EC4E47-914E-4F4C-A2F2-E8EF8EB65CA7}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{13F1BD31-9CE7-42F8-B9C8-39B7921BFE9D}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0300-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{7F3E50A0-5AD4-47B8-BC45-7B3B57645233}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0300-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{125C3C0E-0FAD-422C-993E-5F2DC10EE44A}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0300-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{4FC48642-812B-4C94-9A26-E3C5C048AD35}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0300-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{F9F26F7E-C1D5-40D4-8E34-6517BAE0BC28}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0300-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{5C225C7D-5856-42F0-9180-A64163CA4362}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0300-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{F96E037C-1D28-48E1-8183-92352FF3980A}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0300-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8096,12 +7840,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -8124,7 +7864,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8139,33 +7879,24 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -8195,9 +7926,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -8211,254 +7939,176 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>900</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -8728,39 +8378,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{1540383D-5D73-46E8-B958-7167D49431D3}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{C65FB02E-4430-4C6A-822E-5D13FB8E75EF}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{F018275B-9EE1-4999-ADEE-868F5C273265}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B42 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B16 B38 B34 B25 B20:B21 B18" xr:uid="{EBF17019-D1FE-448A-8D50-67DF4C355FB6}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{6A36766F-79A4-453B-A843-8BD74C4E1DA6}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0400-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{4FFC33FD-93BD-466B-B565-659062E9E06C}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0400-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{BCE6805E-E822-4636-9D8F-5F9A47144DBC}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0400-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{20C7C0E7-F87B-41D9-972D-05C1FE57EE6B}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0400-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B41 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B33 B37" xr:uid="{B6D0B6A5-EB52-45B6-BA75-1FC1C27B94FA}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0400-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B43 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B35 B39" xr:uid="{1F3F3FC2-420F-4706-8F95-8F64B950D904}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0400-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B44 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B36 B40" xr:uid="{418C74AF-5CDC-4538-9ACA-3DC03A47EC1D}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0400-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8770,11 +8480,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -8797,7 +8504,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8812,33 +8519,24 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -8868,9 +8566,6 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -8884,254 +8579,176 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>800</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -9401,39 +9018,99 @@
         <v>109</v>
       </c>
     </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{18F5698D-E9A1-426C-A486-980234631FAA}">
+    <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{60D9E297-CDCE-4E47-876B-CF6B6F93F152}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{E97E72E8-9578-431D-82E9-9CDFC2A00A26}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B42 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B16 B38 B34 B25 B20:B21 B18" xr:uid="{73F5181F-3E77-46CB-AA06-DFFD0607AF37}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0500-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{FF408698-D90D-4324-964F-83BDF9B04138}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0500-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{8BE5220F-D5EF-4178-9E79-141053597457}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0500-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{BC1733B3-E461-4F21-A4E4-4B31BADD4913}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0500-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{A2BECD1B-B9D4-4994-BAFC-9B3BD7AAE87D}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0500-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B41 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B33 B37" xr:uid="{ABB1642B-3712-47DB-BDB9-B78C86D570E4}">
+    <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0500-000012000000}">
       <formula1>"electric,gas,propane,fuel_oil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B43 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B35 B39" xr:uid="{6EF27BCC-8225-46F0-A029-E79C3BBE2629}">
+    <dataValidation type="list" allowBlank="1" sqref="B35 B99 B95 B91 B87 B83 B79 B75 B71 B67 B63 B59 B55 B51 B47 B43 B39" xr:uid="{00000000-0002-0000-0500-000014000000}">
       <formula1>"kwh,mmbtu,nan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B44 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B36 B40" xr:uid="{C6F28F82-E294-44DB-822B-F1590097F42D}">
+    <dataValidation type="list" allowBlank="1" sqref="B36 B100 B96 B92 B88 B84 B80 B76 B72 B68 B64 B60 B56 B52 B48 B44 B40" xr:uid="{00000000-0002-0000-0500-000015000000}">
       <formula1>"appliance,motors,heating,cooling"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9443,11 +9120,8 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9470,7 +9144,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -9478,16 +9152,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -9501,17 +9172,11 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>250</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -9541,270 +9206,189 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>1000</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>1</v>
+      <c r="B24" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -10072,6 +9656,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10088,16 +9732,16 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0600-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{710A08F4-08FD-4A48-916F-F9A6ACE1E4AE}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0600-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{8BEACE89-CED4-461F-BB25-1647EFC83B5C}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0600-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{D853C5CE-AEE7-4F14-9E84-7ADF97A2341C}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0600-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{33742A7C-D4FE-407B-87FA-4EEC50A0F59E}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0600-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0600-000012000000}">
@@ -10116,11 +9760,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="38.85546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -10143,7 +9784,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -10151,40 +9792,31 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -10220,261 +9852,183 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>900</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>1</v>
+      <c r="B24" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -10742,6 +10296,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -10749,25 +10363,25 @@
     <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{7F523F77-192F-4698-B631-CED69F400D1E}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{692F9199-D4AC-4314-A9AF-B623B0633780}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0700-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B34 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B16 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0700-000003000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0700-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{96647A8B-82B4-45F6-BAC7-E4F6D1BE6E06}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0700-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{29B51D28-9930-4F28-A603-6133407275DA}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0700-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{875AD6AA-663C-4B44-A0C3-32F5D4C40092}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0700-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{1A87BF84-0C5C-46DA-9253-DEA03453F8B3}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0700-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0700-000012000000}">
@@ -10786,11 +10400,8 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="36.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -10813,7 +10424,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -10821,40 +10432,31 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>2030</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>2050</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -10884,270 +10486,189 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>750</v>
-      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18">
-        <v>100</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24">
-        <v>1</v>
+      <c r="B24" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25">
-        <v>0.02</v>
-      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="B27" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
-      <c r="B33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
-      <c r="B34">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
-      <c r="B35" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
-      <c r="B38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
-      <c r="B40" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -11415,6 +10936,66 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -11422,25 +11003,25 @@
     <dataValidation type="list" allowBlank="1" sqref="B12" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"heating,cooling,both"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{9ACE1E4E-A605-4040-B46F-DC4E1B5E1AB0}">
+    <dataValidation type="list" allowBlank="1" sqref="B14" xr:uid="{00000000-0002-0000-0800-000001000000}">
       <formula1>"single_family,multifamily,single_family_li,multifamily_li"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{242F86A3-9D52-4AF9-844A-C35C507ED9A7}">
+    <dataValidation type="list" allowBlank="1" sqref="B15" xr:uid="{00000000-0002-0000-0800-000002000000}">
       <formula1>"test,test_2,nan"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B34 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B16 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0800-000003000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a numeric value" sqref="B16 B98 B94 B90 B86 B82 B78 B74 B70 B66 B62 B58 B54 B50 B46 B42 B38 B34 B25 B20:B21 B18" xr:uid="{00000000-0002-0000-0800-000003000000}">
       <formula1>-999999999</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{DC714DF5-F383-464D-9286-1B715BF6736C}">
+    <dataValidation type="list" allowBlank="1" sqref="B17 B32" xr:uid="{00000000-0002-0000-0800-000004000000}">
       <formula1>"Standard,Manual"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{8A026AFE-24E4-43F7-A32C-1BEA611F96AE}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a whole number (integer) greater than or equal to 0" sqref="B19" xr:uid="{00000000-0002-0000-0800-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{4F47616E-2D38-411E-AC88-E9298732573F}">
+    <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{00000000-0002-0000-0800-000009000000}">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B26:B31" xr:uid="{8B876790-5FBE-4020-B3C5-CD79A74235A8}">
+    <dataValidation type="list" allowBlank="1" sqref="B102:B113 B26:B31" xr:uid="{00000000-0002-0000-0800-00000B000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B33 B97 B93 B89 B85 B81 B77 B73 B69 B65 B61 B57 B53 B49 B45 B41 B37" xr:uid="{00000000-0002-0000-0800-000012000000}">

--- a/00_output/workpapers.xlsx
+++ b/00_output/workpapers.xlsx
@@ -468,8 +468,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1735,8 +1735,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3002,8 +3002,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4269,8 +4269,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5536,8 +5536,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6803,8 +6803,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8070,8 +8070,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9337,8 +9337,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10604,8 +10604,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11871,8 +11871,8 @@
   <dimension ref="A1:B114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
